--- a/data/stats/supp_tables/spweedcountsPERENN-anova.xlsx
+++ b/data/stats/supp_tables/spweedcountsPERENN-anova.xlsx
@@ -396,13 +396,13 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D2">
         <v>44.311</v>
       </c>
       <c r="E2">
-        <v>1.068795416931184E-10</v>
+        <v>3.270189633139164E-10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -420,13 +420,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>354</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>1.431</v>
       </c>
       <c r="E3">
-        <v>0.2405408931903086</v>
+        <v>0.2771778660284521</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>354</v>
+        <v>3</v>
       </c>
       <c r="D4">
         <v>0.028</v>
       </c>
       <c r="E4">
-        <v>0.8660923067326427</v>
+        <v>0.8767317214285916</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -468,13 +468,13 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="D5">
         <v>12.744</v>
       </c>
       <c r="E5">
-        <v>1.060920231460809E-09</v>
+        <v>6.800284047625147E-08</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -492,13 +492,13 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D6">
-        <v>3229.24</v>
+        <v>3229.241</v>
       </c>
       <c r="E6">
-        <v>5.203935276373905E-180</v>
+        <v>2.652281377010909E-72</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -516,13 +516,13 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D7">
         <v>19.615</v>
       </c>
       <c r="E7">
-        <v>8.340783896698425E-09</v>
+        <v>1.966095815782024E-08</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -540,13 +540,13 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D8">
         <v>1.593</v>
       </c>
       <c r="E8">
-        <v>0.2077959669060376</v>
+        <v>0.2085978912123115</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D9">
         <v>1.336</v>
       </c>
       <c r="E9">
-        <v>0.2562487242076958</v>
+        <v>0.258461454350982</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -588,13 +588,13 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D10">
         <v>49.266</v>
       </c>
       <c r="E10">
-        <v>1.145892433938195E-11</v>
+        <v>4.397667186315066E-11</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -612,13 +612,13 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>354</v>
+        <v>12</v>
       </c>
       <c r="D11">
         <v>0.871</v>
       </c>
       <c r="E11">
-        <v>0.419561641425549</v>
+        <v>0.4435160537349679</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -636,13 +636,13 @@
         <v>8</v>
       </c>
       <c r="C12">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="D12">
         <v>4.109</v>
       </c>
       <c r="E12">
-        <v>0.0001054889773160705</v>
+        <v>0.0004451734224837624</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -660,13 +660,13 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D13">
         <v>95.607</v>
       </c>
       <c r="E13">
-        <v>6.328456009000135E-34</v>
+        <v>5.423585754182047E-23</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -684,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="D14">
         <v>1.848</v>
       </c>
       <c r="E14">
-        <v>0.1191396901677637</v>
+        <v>0.1290277749740073</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -708,13 +708,13 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D15">
         <v>6.803</v>
       </c>
       <c r="E15">
-        <v>0.009487616342530808</v>
+        <v>0.01065631771485185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -732,13 +732,13 @@
         <v>4</v>
       </c>
       <c r="C16">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D16">
         <v>4.254</v>
       </c>
       <c r="E16">
-        <v>0.002243508407272781</v>
+        <v>0.003366020949006202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -756,13 +756,13 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D17">
         <v>2.014</v>
       </c>
       <c r="E17">
-        <v>0.1349784326507475</v>
+        <v>0.1364484523798616</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -780,13 +780,13 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D18">
         <v>0.627</v>
       </c>
       <c r="E18">
-        <v>0.755050496349732</v>
+        <v>0.7543632474546158</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D19">
         <v>10.554</v>
       </c>
       <c r="E19">
-        <v>3.532200869238243E-05</v>
+        <v>4.634628028587962E-05</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D20">
         <v>0.422</v>
       </c>
       <c r="E20">
-        <v>0.7924269652394444</v>
+        <v>0.7923007872961823</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -852,13 +852,13 @@
         <v>1</v>
       </c>
       <c r="C21">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D21">
         <v>5.048</v>
       </c>
       <c r="E21">
-        <v>0.02526493465910983</v>
+        <v>0.02586406900452108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         <v>4</v>
       </c>
       <c r="C22">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D22">
         <v>6.717</v>
       </c>
       <c r="E22">
-        <v>3.207930318987684E-05</v>
+        <v>4.628172941695366E-05</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -900,13 +900,13 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="D23">
         <v>0.922</v>
       </c>
       <c r="E23">
-        <v>0.4984561783421699</v>
+        <v>0.5039771457369452</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -924,13 +924,13 @@
         <v>2</v>
       </c>
       <c r="C24">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D24">
         <v>0.033</v>
       </c>
       <c r="E24">
-        <v>0.9673722360980621</v>
+        <v>0.9673810449767305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -948,13 +948,13 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D25">
         <v>1.525</v>
       </c>
       <c r="E25">
-        <v>0.1470225269947804</v>
+        <v>0.1596896675897027</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -972,13 +972,13 @@
         <v>4</v>
       </c>
       <c r="C26">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D26">
         <v>1.054</v>
       </c>
       <c r="E26">
-        <v>0.3790958286997187</v>
+        <v>0.3839160983344204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -996,13 +996,13 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D27">
         <v>0.878</v>
       </c>
       <c r="E27">
-        <v>0.5354589276044184</v>
+        <v>0.5364867935129507</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1020,13 +1020,13 @@
         <v>2</v>
       </c>
       <c r="C28">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D28">
         <v>0.673</v>
       </c>
       <c r="E28">
-        <v>0.5110229571428444</v>
+        <v>0.5116499410951649</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>8</v>
       </c>
       <c r="C29">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D29">
         <v>3.052</v>
       </c>
       <c r="E29">
-        <v>0.002463324246037315</v>
+        <v>0.003028306890363522</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1068,13 +1068,13 @@
         <v>4</v>
       </c>
       <c r="C30">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D30">
         <v>1.102</v>
       </c>
       <c r="E30">
-        <v>0.3556013173960978</v>
+        <v>0.3573323031612413</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1092,13 +1092,13 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="D31">
         <v>0.99</v>
       </c>
       <c r="E31">
-        <v>0.4430741123475996</v>
+        <v>0.4489527651627563</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1116,13 +1116,13 @@
         <v>8</v>
       </c>
       <c r="C32">
-        <v>354</v>
+        <v>180</v>
       </c>
       <c r="D32">
         <v>1.732</v>
       </c>
       <c r="E32">
-        <v>0.0897390665210121</v>
+        <v>0.09371253566969581</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
